--- a/Aug_2026/daily Reports/Nabeel Data.xlsx
+++ b/Aug_2026/daily Reports/Nabeel Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA5E32A-CB81-49F9-8443-954B0BB41E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A1589E-A7EE-4AF8-A2CA-FD024369E0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{0C090EE1-522B-482D-ABA5-C884A27BC91F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{0C090EE1-522B-482D-ABA5-C884A27BC91F}"/>
   </bookViews>
   <sheets>
     <sheet name="Akeel " sheetId="1" r:id="rId1"/>
@@ -246,10 +246,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5033,7 +5033,7 @@
         <v>3212</v>
       </c>
       <c r="F257" s="8">
-        <f t="shared" ref="F257:K258" si="0">SUM(F8:F255)</f>
+        <f t="shared" ref="F257:K257" si="0">SUM(F8:F255)</f>
         <v>1273</v>
       </c>
       <c r="G257" s="8">
